--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34967FE8-55D2-4E8E-9537-CD5C168BD97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4B3727-091B-4B42-9829-C2586908A624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9525" yWindow="420" windowWidth="23310" windowHeight="20160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -259,12 +259,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -354,7 +354,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="386"/>
                 <c:pt idx="0">
-                  <c:v>43.158749999999998</c:v>
+                  <c:v>42.825416666666662</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1683,7 +1683,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="386"/>
                 <c:pt idx="0">
-                  <c:v>3.641578947368421</c:v>
+                  <c:v>3.6521052631578947</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -6037,7 +6037,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -6067,7 +6067,7 @@
       <c r="Z1" s="7"/>
     </row>
     <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -6232,7 +6232,7 @@
         <v>45</v>
       </c>
       <c r="S5" s="3">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="T5" s="3">
         <v>37</v>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="Z5" s="4">
         <f t="shared" ref="Z5:Z68" si="0">IF(COUNTA(B5:Y5)=0,"",AVERAGE(B5:Y5))</f>
-        <v>43.158749999999998</v>
+        <v>42.825416666666662</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -18157,7 +18157,7 @@
       <c r="X389" s="3"/>
       <c r="Y389" s="3"/>
       <c r="Z389" s="4" t="str">
-        <f t="shared" ref="Z389:Z452" si="6">IF(COUNTA(B389:Y389)=0,"",AVERAGE(B389:Y389))</f>
+        <f t="shared" ref="Z389:Z390" si="6">IF(COUNTA(B389:Y389)=0,"",AVERAGE(B389:Y389))</f>
         <v/>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="7"/>
@@ -18243,7 +18243,7 @@
       <c r="U1" s="7"/>
     </row>
     <row r="2" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -18361,7 +18361,7 @@
         <v>3.39</v>
       </c>
       <c r="J5" s="3">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="K5" s="3">
         <v>4.09</v>
@@ -18395,7 +18395,7 @@
       </c>
       <c r="U5" s="4">
         <f t="shared" ref="U5:U68" si="0">IF(COUNTA(B5:T5)=0,"",AVERAGE(B5:T5))</f>
-        <v>3.641578947368421</v>
+        <v>3.6521052631578947</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -28378,7 +28378,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U452" si="6">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="6">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -28434,7 +28434,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="7"/>
@@ -28449,7 +28449,7 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -34674,7 +34674,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K452" si="6">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="6">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -34720,7 +34720,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="7"/>
@@ -34736,7 +34736,7 @@
       <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -41352,7 +41352,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L452" si="6">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="6">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>

--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DAAD45-883B-474E-AA16-EA8A405FFB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33E78CB-E827-417B-AD04-F2A1A22F29CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59640" yWindow="2925" windowWidth="17265" windowHeight="15495" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -259,12 +259,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -345,6 +345,9 @@
                   <c:v>46123</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
@@ -363,7 +366,7 @@
                   <c:v>42.825416666666662</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>42.825416666666662</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1677,6 +1680,9 @@
                   <c:v>46123</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
@@ -1695,7 +1701,7 @@
                   <c:v>3.6521052631578947</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.642631578947368</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3009,6 +3015,9 @@
                   <c:v>46123</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
@@ -3027,7 +3036,7 @@
                   <c:v>2.818888888888889</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.818888888888889</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4341,6 +4350,9 @@
                   <c:v>46123</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
@@ -4359,7 +4371,7 @@
                   <c:v>3.3450000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.3450000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -6049,7 +6061,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -6079,7 +6091,7 @@
       <c r="Z1" s="7"/>
     </row>
     <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -6271,7 +6283,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="B6" s="3">
         <v>43</v>
@@ -6351,34 +6363,84 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="4" t="str">
+      <c r="A7" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B7" s="3">
+        <v>43</v>
+      </c>
+      <c r="C7" s="3">
+        <v>45</v>
+      </c>
+      <c r="D7" s="3">
+        <v>45</v>
+      </c>
+      <c r="E7" s="3">
+        <v>45</v>
+      </c>
+      <c r="F7" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G7" s="3">
+        <v>39.5</v>
+      </c>
+      <c r="H7" s="3">
+        <v>46</v>
+      </c>
+      <c r="I7" s="3">
+        <v>42</v>
+      </c>
+      <c r="J7" s="3">
+        <v>43</v>
+      </c>
+      <c r="K7" s="3">
+        <v>40</v>
+      </c>
+      <c r="L7" s="3">
+        <v>36</v>
+      </c>
+      <c r="M7" s="3">
+        <v>44</v>
+      </c>
+      <c r="N7" s="3">
+        <v>45</v>
+      </c>
+      <c r="O7" s="3">
+        <v>46.06</v>
+      </c>
+      <c r="P7" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>45</v>
+      </c>
+      <c r="R7" s="3">
+        <v>45</v>
+      </c>
+      <c r="S7" s="3">
+        <v>37</v>
+      </c>
+      <c r="T7" s="3">
+        <v>37</v>
+      </c>
+      <c r="U7" s="3">
+        <v>43</v>
+      </c>
+      <c r="V7" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W7" s="3">
+        <v>42</v>
+      </c>
+      <c r="X7" s="3">
+        <v>46</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z7" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>42.825416666666662</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -18280,7 +18342,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="7"/>
@@ -18305,7 +18367,7 @@
       <c r="U1" s="7"/>
     </row>
     <row r="2" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -18462,7 +18524,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="B6" s="3">
         <v>4.29</v>
@@ -18527,29 +18589,69 @@
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="4" t="str">
+      <c r="A7" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B7" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J7" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K7" s="3">
+        <v>4.09</v>
+      </c>
+      <c r="L7" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M7" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N7" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O7" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P7" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R7" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S7" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T7" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U7" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.642631578947368</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -28536,7 +28638,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="7"/>
@@ -28551,7 +28653,7 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -28638,7 +28740,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="B6" s="3">
         <v>2.85</v>
@@ -28673,19 +28775,39 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4" t="str">
+      <c r="A7" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I7" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J7" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K7" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.818888888888889</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -34842,7 +34964,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="7"/>
@@ -34858,7 +34980,7 @@
       <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -34952,7 +35074,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="B6" s="3">
         <v>3.69</v>
@@ -34990,20 +35112,42 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="4" t="str">
+      <c r="A7" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B7" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H7" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="J7" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K7" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L7" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3450000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33E78CB-E827-417B-AD04-F2A1A22F29CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA1A527-256A-4C66-AF77-C5014FE4659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59640" yWindow="2925" windowWidth="17265" windowHeight="15495" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16980" yWindow="1680" windowWidth="21405" windowHeight="15495" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -259,12 +259,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -350,6 +350,9 @@
                 <c:pt idx="2">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -369,7 +372,7 @@
                   <c:v>42.825416666666662</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>43.248333333333335</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1685,6 +1688,9 @@
                 <c:pt idx="2">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1704,7 +1710,7 @@
                   <c:v>3.642631578947368</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -3020,6 +3026,9 @@
                 <c:pt idx="2">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3039,7 +3048,7 @@
                   <c:v>2.818888888888889</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -4355,6 +4364,9 @@
                 <c:pt idx="2">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4374,7 +4386,7 @@
                   <c:v>3.3450000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.3240000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -6061,7 +6073,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -6091,7 +6103,7 @@
       <c r="Z1" s="7"/>
     </row>
     <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -6444,34 +6456,84 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="4" t="str">
+      <c r="A8" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B8" s="3">
+        <v>43</v>
+      </c>
+      <c r="C8" s="3">
+        <v>45</v>
+      </c>
+      <c r="D8" s="3">
+        <v>45</v>
+      </c>
+      <c r="E8" s="3">
+        <v>45</v>
+      </c>
+      <c r="F8" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G8" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H8" s="3">
+        <v>46</v>
+      </c>
+      <c r="I8" s="3">
+        <v>42</v>
+      </c>
+      <c r="J8" s="3">
+        <v>43</v>
+      </c>
+      <c r="K8" s="3">
+        <v>40</v>
+      </c>
+      <c r="L8" s="3">
+        <v>36</v>
+      </c>
+      <c r="M8" s="3">
+        <v>44</v>
+      </c>
+      <c r="N8" s="3">
+        <v>45</v>
+      </c>
+      <c r="O8" s="3">
+        <v>46.21</v>
+      </c>
+      <c r="P8" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>45</v>
+      </c>
+      <c r="R8" s="3">
+        <v>45</v>
+      </c>
+      <c r="S8" s="3">
+        <v>45</v>
+      </c>
+      <c r="T8" s="3">
+        <v>37</v>
+      </c>
+      <c r="U8" s="3">
+        <v>43</v>
+      </c>
+      <c r="V8" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W8" s="3">
+        <v>42</v>
+      </c>
+      <c r="X8" s="3">
+        <v>46</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z8" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.248333333333335</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -18342,7 +18404,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="7"/>
@@ -18367,7 +18429,7 @@
       <c r="U1" s="7"/>
     </row>
     <row r="2" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -18655,29 +18717,69 @@
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="4" t="str">
+      <c r="A8" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B8" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K8" s="3">
+        <v>4.09</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N8" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O8" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P8" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R8" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S8" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T8" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U8" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5973684210526313</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -28638,7 +28740,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="7"/>
@@ -28653,7 +28755,7 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -28811,19 +28913,39 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4" t="str">
+      <c r="A8" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K8" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -34964,7 +35086,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="7"/>
@@ -34980,7 +35102,7 @@
       <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -35151,20 +35273,42 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="4" t="str">
+      <c r="A8" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B8" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L8" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3240000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA1A527-256A-4C66-AF77-C5014FE4659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BCAFB2-835F-4266-882B-91311123A748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16980" yWindow="1680" windowWidth="21405" windowHeight="15495" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10515" yWindow="2940" windowWidth="26490" windowHeight="15495" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -353,6 +353,9 @@
                 <c:pt idx="3">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -375,7 +378,7 @@
                   <c:v>43.248333333333335</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>43.085416666666667</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -1691,6 +1694,9 @@
                 <c:pt idx="3">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1713,7 +1719,7 @@
                   <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -3029,6 +3035,9 @@
                 <c:pt idx="3">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3051,7 +3060,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -4367,6 +4376,9 @@
                 <c:pt idx="3">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4389,7 +4401,7 @@
                   <c:v>3.3240000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3.3240000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -6537,34 +6549,84 @@
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="4" t="str">
+      <c r="A9" s="2">
+        <v>46128</v>
+      </c>
+      <c r="B9" s="3">
+        <v>43</v>
+      </c>
+      <c r="C9" s="3">
+        <v>45</v>
+      </c>
+      <c r="D9" s="3">
+        <v>45</v>
+      </c>
+      <c r="E9" s="3">
+        <v>45</v>
+      </c>
+      <c r="F9" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46</v>
+      </c>
+      <c r="I9" s="3">
+        <v>42</v>
+      </c>
+      <c r="J9" s="3">
+        <v>43</v>
+      </c>
+      <c r="K9" s="3">
+        <v>40</v>
+      </c>
+      <c r="L9" s="3">
+        <v>36</v>
+      </c>
+      <c r="M9" s="3">
+        <v>44</v>
+      </c>
+      <c r="N9" s="3">
+        <v>45</v>
+      </c>
+      <c r="O9" s="3">
+        <v>42.3</v>
+      </c>
+      <c r="P9" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>45</v>
+      </c>
+      <c r="R9" s="3">
+        <v>45</v>
+      </c>
+      <c r="S9" s="3">
+        <v>45</v>
+      </c>
+      <c r="T9" s="3">
+        <v>37</v>
+      </c>
+      <c r="U9" s="3">
+        <v>43</v>
+      </c>
+      <c r="V9" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W9" s="3">
+        <v>42</v>
+      </c>
+      <c r="X9" s="3">
+        <v>46</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z9" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.085416666666667</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -18783,29 +18845,69 @@
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="4" t="str">
+      <c r="A9" s="2">
+        <v>46128</v>
+      </c>
+      <c r="B9" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K9" s="3">
+        <v>4.09</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M9" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N9" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O9" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P9" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R9" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S9" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T9" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U9" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5973684210526313</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -28949,19 +29051,39 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4" t="str">
+      <c r="A9" s="2">
+        <v>46128</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K9" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -35312,20 +35434,42 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="4" t="str">
+      <c r="A9" s="2">
+        <v>46128</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L9" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3240000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BCAFB2-835F-4266-882B-91311123A748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54402698-EEB8-41A3-85D1-971D2ECCC296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10515" yWindow="2940" windowWidth="26490" windowHeight="15495" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7875" yWindow="1170" windowWidth="29610" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -356,6 +356,9 @@
                 <c:pt idx="4">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -381,7 +384,7 @@
                   <c:v>43.085416666666667</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>43.127083333333331</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -1697,6 +1700,9 @@
                 <c:pt idx="4">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1722,7 +1728,7 @@
                   <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -3038,6 +3044,9 @@
                 <c:pt idx="4">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3063,7 +3072,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -4379,6 +4388,9 @@
                 <c:pt idx="4">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4404,7 +4416,7 @@
                   <c:v>3.3240000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3.3240000000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -6630,34 +6642,84 @@
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="4" t="str">
+      <c r="A10" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B10" s="3">
+        <v>43</v>
+      </c>
+      <c r="C10" s="3">
+        <v>45</v>
+      </c>
+      <c r="D10" s="3">
+        <v>45</v>
+      </c>
+      <c r="E10" s="3">
+        <v>45</v>
+      </c>
+      <c r="F10" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G10" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>46</v>
+      </c>
+      <c r="I10" s="3">
+        <v>42</v>
+      </c>
+      <c r="J10" s="3">
+        <v>43</v>
+      </c>
+      <c r="K10" s="3">
+        <v>41</v>
+      </c>
+      <c r="L10" s="3">
+        <v>36</v>
+      </c>
+      <c r="M10" s="3">
+        <v>44</v>
+      </c>
+      <c r="N10" s="3">
+        <v>45</v>
+      </c>
+      <c r="O10" s="3">
+        <v>42.3</v>
+      </c>
+      <c r="P10" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>45</v>
+      </c>
+      <c r="R10" s="3">
+        <v>45</v>
+      </c>
+      <c r="S10" s="3">
+        <v>45</v>
+      </c>
+      <c r="T10" s="3">
+        <v>37</v>
+      </c>
+      <c r="U10" s="3">
+        <v>43</v>
+      </c>
+      <c r="V10" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W10" s="3">
+        <v>42</v>
+      </c>
+      <c r="X10" s="3">
+        <v>46</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z10" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.127083333333331</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -18911,29 +18973,69 @@
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="4" t="str">
+      <c r="A10" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B10" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K10" s="3">
+        <v>4.09</v>
+      </c>
+      <c r="L10" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M10" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N10" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O10" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P10" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R10" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S10" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U10" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5973684210526313</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -29087,19 +29189,39 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4" t="str">
+      <c r="A10" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K10" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -35473,20 +35595,42 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="4" t="str">
+      <c r="A10" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B10" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L10" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3240000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54402698-EEB8-41A3-85D1-971D2ECCC296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4FAE5E-A956-498C-B7D2-5BAFF8D6E7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7875" yWindow="1170" windowWidth="29610" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10590" yWindow="1680" windowWidth="27720" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -359,6 +359,9 @@
                 <c:pt idx="5">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -387,7 +390,7 @@
                   <c:v>43.127083333333331</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>43.085416666666667</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -1703,6 +1706,9 @@
                 <c:pt idx="5">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1731,7 +1737,7 @@
                   <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -3047,6 +3053,9 @@
                 <c:pt idx="5">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3075,7 +3084,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -4391,6 +4400,9 @@
                 <c:pt idx="5">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4419,7 +4431,7 @@
                   <c:v>3.3240000000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>3.3240000000000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -6723,34 +6735,84 @@
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="4" t="str">
+      <c r="A11" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B11" s="3">
+        <v>42</v>
+      </c>
+      <c r="C11" s="3">
+        <v>45</v>
+      </c>
+      <c r="D11" s="3">
+        <v>45</v>
+      </c>
+      <c r="E11" s="3">
+        <v>45</v>
+      </c>
+      <c r="F11" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G11" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46</v>
+      </c>
+      <c r="I11" s="3">
+        <v>42</v>
+      </c>
+      <c r="J11" s="3">
+        <v>43</v>
+      </c>
+      <c r="K11" s="3">
+        <v>41</v>
+      </c>
+      <c r="L11" s="3">
+        <v>36</v>
+      </c>
+      <c r="M11" s="3">
+        <v>44</v>
+      </c>
+      <c r="N11" s="3">
+        <v>45</v>
+      </c>
+      <c r="O11" s="3">
+        <v>42.3</v>
+      </c>
+      <c r="P11" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>45</v>
+      </c>
+      <c r="R11" s="3">
+        <v>45</v>
+      </c>
+      <c r="S11" s="3">
+        <v>45</v>
+      </c>
+      <c r="T11" s="3">
+        <v>37</v>
+      </c>
+      <c r="U11" s="3">
+        <v>43</v>
+      </c>
+      <c r="V11" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W11" s="3">
+        <v>42</v>
+      </c>
+      <c r="X11" s="3">
+        <v>46</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z11" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.085416666666667</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -19039,29 +19101,69 @@
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="4" t="str">
+      <c r="A11" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B11" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H11" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I11" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K11" s="3">
+        <v>4.09</v>
+      </c>
+      <c r="L11" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M11" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N11" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O11" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P11" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R11" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S11" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T11" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U11" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5973684210526313</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -29225,19 +29327,39 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4" t="str">
+      <c r="A11" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G11" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H11" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I11" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J11" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K11" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -35634,20 +35756,42 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="4" t="str">
+      <c r="A11" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B11" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H11" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I11" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L11" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3240000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4FAE5E-A956-498C-B7D2-5BAFF8D6E7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD81A42-C55F-4F27-A097-78EEBE6565E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10590" yWindow="1680" windowWidth="27720" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9060" yWindow="1680" windowWidth="29250" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -362,6 +362,9 @@
                 <c:pt idx="6">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -393,7 +396,7 @@
                   <c:v>43.085416666666667</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>43.078749999999992</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1709,6 +1712,9 @@
                 <c:pt idx="6">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1740,7 +1746,7 @@
                   <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3056,6 +3062,9 @@
                 <c:pt idx="6">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3087,7 +3096,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4403,6 +4412,9 @@
                 <c:pt idx="6">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4434,7 +4446,7 @@
                   <c:v>3.3240000000000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6816,34 +6828,84 @@
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="4" t="str">
+      <c r="A12" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B12" s="3">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3">
+        <v>45</v>
+      </c>
+      <c r="D12" s="3">
+        <v>45</v>
+      </c>
+      <c r="E12" s="3">
+        <v>45</v>
+      </c>
+      <c r="F12" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G12" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H12" s="3">
+        <v>46</v>
+      </c>
+      <c r="I12" s="3">
+        <v>42</v>
+      </c>
+      <c r="J12" s="3">
+        <v>43</v>
+      </c>
+      <c r="K12" s="3">
+        <v>41</v>
+      </c>
+      <c r="L12" s="3">
+        <v>36</v>
+      </c>
+      <c r="M12" s="3">
+        <v>44</v>
+      </c>
+      <c r="N12" s="3">
+        <v>45</v>
+      </c>
+      <c r="O12" s="3">
+        <v>42.39</v>
+      </c>
+      <c r="P12" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>45</v>
+      </c>
+      <c r="R12" s="3">
+        <v>45</v>
+      </c>
+      <c r="S12" s="3">
+        <v>45</v>
+      </c>
+      <c r="T12" s="3">
+        <v>37</v>
+      </c>
+      <c r="U12" s="3">
+        <v>43</v>
+      </c>
+      <c r="V12" s="3">
+        <v>44.25</v>
+      </c>
+      <c r="W12" s="3">
+        <v>42</v>
+      </c>
+      <c r="X12" s="3">
+        <v>46</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z12" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.078749999999992</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -19167,29 +19229,69 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="4" t="str">
+      <c r="A12" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B12" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K12" s="3">
+        <v>4.09</v>
+      </c>
+      <c r="L12" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M12" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N12" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O12" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P12" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R12" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S12" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U12" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5973684210526313</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -29363,19 +29465,39 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4" t="str">
+      <c r="A12" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K12" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -35795,20 +35917,42 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="4" t="str">
+      <c r="A12" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B12" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L12" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD81A42-C55F-4F27-A097-78EEBE6565E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B325CD-71D6-46F5-B6DD-B094433378E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="1680" windowWidth="29250" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,6 +365,9 @@
                 <c:pt idx="7">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -399,7 +402,7 @@
                   <c:v>43.078749999999992</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>43.109999999999992</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -1715,6 +1718,9 @@
                 <c:pt idx="7">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1749,7 +1755,7 @@
                   <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -3065,6 +3071,9 @@
                 <c:pt idx="7">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3099,7 +3108,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -4415,6 +4424,9 @@
                 <c:pt idx="7">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4449,7 +4461,7 @@
                   <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6909,34 +6921,84 @@
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="4" t="str">
+      <c r="A13" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B13" s="3">
+        <v>42</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46</v>
+      </c>
+      <c r="D13" s="3">
+        <v>45</v>
+      </c>
+      <c r="E13" s="3">
+        <v>45</v>
+      </c>
+      <c r="F13" s="3">
+        <v>44.25</v>
+      </c>
+      <c r="G13" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H13" s="3">
+        <v>46</v>
+      </c>
+      <c r="I13" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J13" s="3">
+        <v>43</v>
+      </c>
+      <c r="K13" s="3">
+        <v>41</v>
+      </c>
+      <c r="L13" s="3">
+        <v>36</v>
+      </c>
+      <c r="M13" s="3">
+        <v>44</v>
+      </c>
+      <c r="N13" s="3">
+        <v>45</v>
+      </c>
+      <c r="O13" s="3">
+        <v>42.39</v>
+      </c>
+      <c r="P13" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>45</v>
+      </c>
+      <c r="R13" s="3">
+        <v>45</v>
+      </c>
+      <c r="S13" s="3">
+        <v>45</v>
+      </c>
+      <c r="T13" s="3">
+        <v>37</v>
+      </c>
+      <c r="U13" s="3">
+        <v>43</v>
+      </c>
+      <c r="V13" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="W13" s="3">
+        <v>42</v>
+      </c>
+      <c r="X13" s="3">
+        <v>46</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z13" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.109999999999992</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
@@ -19295,29 +19357,69 @@
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="4" t="str">
+      <c r="A13" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B13" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G13" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H13" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I13" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J13" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K13" s="3">
+        <v>4.09</v>
+      </c>
+      <c r="L13" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M13" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N13" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O13" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P13" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R13" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S13" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T13" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U13" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5973684210526313</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -29501,19 +29603,39 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4" t="str">
+      <c r="A13" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G13" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H13" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I13" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J13" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K13" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -35956,20 +36078,42 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="4" t="str">
+      <c r="A13" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B13" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G13" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H13" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I13" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J13" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K13" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L13" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.31</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B325CD-71D6-46F5-B6DD-B094433378E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82C2B47-BF25-4F41-9FA3-5E3FFB736A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="1680" windowWidth="29250" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -368,6 +368,9 @@
                 <c:pt idx="8">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -405,7 +408,7 @@
                   <c:v>43.109999999999992</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>43.443333333333328</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -1721,6 +1724,9 @@
                 <c:pt idx="8">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1758,7 +1764,7 @@
                   <c:v>3.5973684210526313</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>3.5499999999999994</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -3074,6 +3080,9 @@
                 <c:pt idx="8">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3111,7 +3120,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -4427,6 +4436,9 @@
                 <c:pt idx="8">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4464,7 +4476,7 @@
                   <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -7002,34 +7014,84 @@
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="4" t="str">
+      <c r="A14" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B14" s="3">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46</v>
+      </c>
+      <c r="D14" s="3">
+        <v>45</v>
+      </c>
+      <c r="E14" s="3">
+        <v>45</v>
+      </c>
+      <c r="F14" s="3">
+        <v>44.25</v>
+      </c>
+      <c r="G14" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>46</v>
+      </c>
+      <c r="I14" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>43</v>
+      </c>
+      <c r="K14" s="3">
+        <v>41</v>
+      </c>
+      <c r="L14" s="3">
+        <v>36</v>
+      </c>
+      <c r="M14" s="3">
+        <v>44</v>
+      </c>
+      <c r="N14" s="3">
+        <v>45</v>
+      </c>
+      <c r="O14" s="3">
+        <v>42.39</v>
+      </c>
+      <c r="P14" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>45</v>
+      </c>
+      <c r="R14" s="3">
+        <v>45</v>
+      </c>
+      <c r="S14" s="3">
+        <v>45</v>
+      </c>
+      <c r="T14" s="3">
+        <v>45</v>
+      </c>
+      <c r="U14" s="3">
+        <v>43</v>
+      </c>
+      <c r="V14" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="W14" s="3">
+        <v>42</v>
+      </c>
+      <c r="X14" s="3">
+        <v>46</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z14" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.443333333333328</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
@@ -19423,29 +19485,69 @@
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="4" t="str">
+      <c r="A14" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B14" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G14" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K14" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="M14" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N14" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O14" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R14" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S14" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T14" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U14" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5499999999999994</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -29639,19 +29741,39 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4" t="str">
+      <c r="A14" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G14" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K14" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -36117,20 +36239,42 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="4" t="str">
+      <c r="A14" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G14" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L14" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.31</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/public/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82C2B47-BF25-4F41-9FA3-5E3FFB736A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339FE24B-4581-4146-B23E-B98F473021A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="1680" windowWidth="29250" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,6 +371,9 @@
                 <c:pt idx="9">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -411,7 +414,7 @@
                   <c:v>43.443333333333328</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>43.432916666666664</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -1727,6 +1730,9 @@
                 <c:pt idx="9">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1767,7 +1773,7 @@
                   <c:v>3.5499999999999994</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>3.5499999999999994</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -3083,6 +3089,9 @@
                 <c:pt idx="9">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3123,7 +3132,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -4439,6 +4448,9 @@
                 <c:pt idx="9">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4479,7 +4491,7 @@
                   <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -7095,34 +7107,84 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="4" t="str">
+      <c r="A15" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B15" s="3">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46</v>
+      </c>
+      <c r="D15" s="3">
+        <v>45</v>
+      </c>
+      <c r="E15" s="3">
+        <v>45</v>
+      </c>
+      <c r="F15" s="3">
+        <v>44.25</v>
+      </c>
+      <c r="G15" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H15" s="3">
+        <v>46</v>
+      </c>
+      <c r="I15" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J15" s="3">
+        <v>43</v>
+      </c>
+      <c r="K15" s="3">
+        <v>41</v>
+      </c>
+      <c r="L15" s="3">
+        <v>36</v>
+      </c>
+      <c r="M15" s="3">
+        <v>44</v>
+      </c>
+      <c r="N15" s="3">
+        <v>45</v>
+      </c>
+      <c r="O15" s="3">
+        <v>42.39</v>
+      </c>
+      <c r="P15" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>45</v>
+      </c>
+      <c r="R15" s="3">
+        <v>45</v>
+      </c>
+      <c r="S15" s="3">
+        <v>45</v>
+      </c>
+      <c r="T15" s="3">
+        <v>45</v>
+      </c>
+      <c r="U15" s="3">
+        <v>43</v>
+      </c>
+      <c r="V15" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="W15" s="3">
+        <v>42</v>
+      </c>
+      <c r="X15" s="3">
+        <v>46</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z15" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.432916666666664</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -19551,29 +19613,69 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="4" t="str">
+      <c r="A15" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B15" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I15" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K15" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L15" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="M15" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N15" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O15" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P15" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R15" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S15" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U15" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5499999999999994</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -29777,19 +29879,39 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4" t="str">
+      <c r="A15" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G15" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K15" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -36278,20 +36400,42 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="4" t="str">
+      <c r="A15" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B15" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H15" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I15" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K15" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L15" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
